--- a/TESTING/src/test/resources/testdata/UI_AuthData.xlsx
+++ b/TESTING/src/test/resources/testdata/UI_AuthData.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Registration" r:id="rId3" sheetId="1"/>
     <sheet name="Login" r:id="rId4" sheetId="2"/>
+    <sheet name="Defaults" r:id="rId5" sheetId="3"/>
+    <sheet name="AdminCreate" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="94">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -259,6 +261,42 @@
   </si>
   <si>
     <t>Wrong role / creds combo</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>DefaultPassword</t>
+  </si>
+  <si>
+    <t>Shared password for auto-registered customers/sellers</t>
+  </si>
+  <si>
+    <t>DefaultPhone</t>
+  </si>
+  <si>
+    <t>Shared phone for auto-registered customers/sellers</t>
+  </si>
+  <si>
+    <t>TC069</t>
+  </si>
+  <si>
+    <t>KNOWN_BUG</t>
+  </si>
+  <si>
+    <t>TestAdmin</t>
+  </si>
+  <si>
+    <t>testadmin@zuply.in</t>
+  </si>
+  <si>
+    <t>Admin@123</t>
+  </si>
+  <si>
+    <t>Backend api/admin/create-admin not implemented (known bug)</t>
   </si>
 </sst>
 </file>
@@ -761,4 +799,103 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>